--- a/Берта Эллинг/13_Тендер/БЭ-ТД ВОР коробки для тендера.xlsx
+++ b/Берта Эллинг/13_Тендер/БЭ-ТД ВОР коробки для тендера.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Сваи ЖБ С80.30 (8 м) с забивкой, 77 шт.</t>
+          <t>Сваи ЖБ С80.30 (8 м) с забивкой, 82 шт.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>513.5700000000001</v>
+        <v>513.1900000000001</v>
       </c>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>154.1</v>
+        <v>154</v>
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
@@ -940,7 +940,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Колонны 1 этажа: стальные с огнезащитой R150 (A) / монолит ЖБ 400×400 (B, C)</t>
+          <t>Колонны 1 этажа: стальные по ЭП с огнезащитой R150 (A) / монолит ЖБ 400×400 (B, C)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Межэтажное и под плоскую кровлю: монолит ЖБ плита 200 + рёбра 600 (A, B) / ПБ + монолитные участки (C)</t>
+          <t>Перекрытие 1 этажа и под плоскую кровлю: монолит ЖБ ребристое, плита 250/200 (A, B) / ПБ + монолитные участки (C)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>798.74</v>
+        <v>945.59</v>
       </c>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Наружные стены газобетон D500 400 мм (блок, клей, армирование, кладка)</t>
+          <t>Наружные стены газобетон D400 400 мм (блок, клей, армирование, кладка)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>309.14</v>
+        <v>257.56</v>
       </c>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>153.54</v>
+        <v>147.21</v>
       </c>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>57.47</v>
+        <v>44.25</v>
       </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>473.73</v>
+        <v>353.6</v>
       </c>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Скатная кровля: стропила, ОСП, мембраны, кликфальц, водосток, снегозадержание</t>
+          <t>Скатная кровля 10°: стропила, ОСП, мембраны, Кликфальц Pro, водосток, снегозадержание</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>570.9299999999999</v>
+        <v>448.03</v>
       </c>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Плоская кровля: эксплуатируемая (A, B) / неэксплуатируемая (C)</t>
+          <t>Плоская кровля неэксплуатируемая: уклоны, утепление XPS 200, мембрана, примыкания</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>233.34</v>
+        <v>339.91</v>
       </c>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Каркасные фронтоны</t>
+          <t>Каркасные стены чердака (фронтоны) 200 мм с фальцем</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>186.21</v>
+        <v>51.72</v>
       </c>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>

--- a/Берта Эллинг/13_Тендер/БЭ-ТД ВОР коробки для тендера.xlsx
+++ b/Берта Эллинг/13_Тендер/БЭ-ТД ВОР коробки для тендера.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Монолитная лестница 012 с ограждением</t>
+          <t>Монолитная лестница 010 с ограждением</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
